--- a/data/trans_bre/P3A_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R2-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,82</t>
+          <t>-0,66; 1,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,55</t>
+          <t>-0,55; 3,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,17</t>
+          <t>-1,15; 3,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,75</t>
+          <t>0,67; 6,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 106,5</t>
+          <t>-24,11; 126,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 79,94</t>
+          <t>-8,82; 83,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 90,68</t>
+          <t>-20,29; 90,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 77,83</t>
+          <t>5,29; 75,37</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,56</t>
+          <t>-1,56; 0,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,9</t>
+          <t>-0,99; 0,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,8</t>
+          <t>-0,71; 0,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,95</t>
+          <t>-1,08; 1,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,07; 33,35</t>
+          <t>-54,24; 24,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 67,14</t>
+          <t>-44,01; 56,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 85,85</t>
+          <t>-46,78; 91,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,03; 57,83</t>
+          <t>-38,46; 60,92</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,15; -0,39</t>
+          <t>-8,03; 0,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 2,91</t>
+          <t>-4,41; 2,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,7</t>
+          <t>-1,78; 3,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,98</t>
+          <t>-3,08; 1,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,83; -3,53</t>
+          <t>-53,66; 1,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-44,55; 43,85</t>
+          <t>-41,68; 44,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-35,44; 128,6</t>
+          <t>-36,56; 128,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 36,47</t>
+          <t>-35,04; 31,65</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,0</t>
+          <t>-1,84; 0,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,71</t>
+          <t>-0,33; 1,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,38</t>
+          <t>-0,3; 1,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,4</t>
+          <t>-0,12; 2,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 1,25</t>
+          <t>-40,49; 1,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 50,94</t>
+          <t>-8,04; 51,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 67,86</t>
+          <t>-10,32; 66,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 65,06</t>
+          <t>-1,45; 62,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R2-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,74</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,96</t>
+          <t>-0,74; 1,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,58</t>
+          <t>-0,82; 3,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,15</t>
+          <t>-1,25; 3,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,57</t>
+          <t>1,37; 6,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 126,49</t>
+          <t>-27,0; 112,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 83,13</t>
+          <t>-12,56; 81,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 90,12</t>
+          <t>-23,11; 87,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 75,37</t>
+          <t>10,57; 83,31</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-2,21%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,42</t>
+          <t>-1,57; 0,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,79</t>
+          <t>-0,99; 0,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,79</t>
+          <t>-0,71; 0,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,02</t>
+          <t>-0,89; 0,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,24; 24,57</t>
+          <t>-54,17; 24,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,01; 56,57</t>
+          <t>-42,63; 62,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,78; 91,09</t>
+          <t>-49,25; 93,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,46; 60,92</t>
+          <t>-29,9; 48,42</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-7,32%</t>
+          <t>-5,3%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 0,14</t>
+          <t>-8,23; -0,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 2,95</t>
+          <t>-4,81; 3,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,5</t>
+          <t>-1,96; 3,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,81</t>
+          <t>-3,13; 1,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,66; 1,94</t>
+          <t>-55,65; -4,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,68; 44,78</t>
+          <t>-45,67; 45,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 128,25</t>
+          <t>-38,14; 133,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-35,04; 31,65</t>
+          <t>-36,32; 34,07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,05</t>
+          <t>-1,9; -0,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,75</t>
+          <t>-0,39; 1,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,38</t>
+          <t>-0,27; 1,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 2,21</t>
+          <t>0,23; 2,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,49; 1,59</t>
+          <t>-40,95; -0,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 51,67</t>
+          <t>-8,63; 46,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 66,77</t>
+          <t>-9,59; 71,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 62,16</t>
+          <t>3,84; 53,82</t>
         </is>
       </c>
     </row>
